--- a/public/templates/digital/Extintores.xlsx
+++ b/public/templates/digital/Extintores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlcan\Desktop\Seguimiento de plataforma de seguridad Antigravity\ssoma-platform\public\templates\digital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEC59C6B-9A6D-48C3-AE0E-F4180510E307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC86FAD-F242-4C16-AD06-360161C14002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11385" windowHeight="7215" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F-SIG-015" sheetId="1" r:id="rId1"/>
@@ -34,8 +34,33 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -337,7 +362,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -563,6 +588,63 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -572,68 +654,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,61 +677,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>204108</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>65311</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1592035</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect l="3186" t="10559" r="60020" b="52795"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="204108" y="65311"/>
-          <a:ext cx="1387927" cy="669475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1000,39 +1032,41 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:XDU54"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="16.2" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32.140625" style="1" customWidth="1"/>
-    <col min="2" max="6" width="19.85546875" style="1" customWidth="1"/>
-    <col min="7" max="9" width="15.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="39.140625" style="1" customWidth="1"/>
-    <col min="11" max="16334" width="11.42578125" style="1"/>
-    <col min="16335" max="16335" width="38.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16336" max="16336" width="42.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16337" max="16337" width="50.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16338" max="16338" width="48.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16339" max="16339" width="48.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16340" max="16340" width="81.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16341" max="16341" width="94.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16342" max="16342" width="45.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16343" max="16344" width="11.42578125" style="1"/>
-    <col min="16345" max="16345" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16346" max="16348" width="11.42578125" style="1"/>
-    <col min="16349" max="16349" width="28.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16350" max="16384" width="28.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" style="1" customWidth="1"/>
+    <col min="2" max="6" width="19.88671875" style="1" customWidth="1"/>
+    <col min="7" max="9" width="15.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="39.109375" style="1" customWidth="1"/>
+    <col min="11" max="16334" width="11.44140625" style="1"/>
+    <col min="16335" max="16335" width="38.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16336" max="16336" width="42.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16337" max="16337" width="50.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16338" max="16338" width="48.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16339" max="16339" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16340" max="16340" width="81.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16341" max="16341" width="94.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16342" max="16342" width="45.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16343" max="16344" width="11.44140625" style="1"/>
+    <col min="16345" max="16345" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16346" max="16348" width="11.44140625" style="1"/>
+    <col min="16349" max="16349" width="28.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16350" max="16384" width="28.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10 16335:16349" ht="29.25" customHeight="1">
-      <c r="A1" s="28"/>
-      <c r="B1" s="26" t="s">
+    <row r="1" spans="1:10 16335:16349" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="47" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="I1" s="10" t="s">
         <v>1</v>
       </c>
@@ -1064,15 +1098,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10 16335:16349" ht="29.25" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+    <row r="2" spans="1:10 16335:16349" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="47"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
       <c r="I2" s="10" t="s">
         <v>11</v>
       </c>
@@ -1113,17 +1147,17 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:10 16335:16349" ht="6.75" customHeight="1">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
+    <row r="3" spans="1:10 16335:16349" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
       <c r="XDG3" s="7" t="s">
         <v>24</v>
       </c>
@@ -1161,23 +1195,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10 16335:16349" s="4" customFormat="1" ht="39" customHeight="1">
+    <row r="4" spans="1:10 16335:16349" s="4" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>36</v>
       </c>
       <c r="B4" s="19"/>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="33"/>
+      <c r="D4" s="34"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="42"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="44"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="32"/>
       <c r="XDG4" s="4" t="s">
         <v>39</v>
       </c>
@@ -1215,25 +1249,25 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:10 16335:16349" s="24" customFormat="1" ht="39" customHeight="1">
-      <c r="A5" s="32" t="s">
+    <row r="5" spans="1:10 16335:16349" s="24" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="32" t="s">
+      <c r="B5" s="34"/>
+      <c r="C5" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32" t="s">
+      <c r="D5" s="34"/>
+      <c r="E5" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="47" t="s">
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="42"/>
+      <c r="J5" s="30"/>
       <c r="XDG5" s="4"/>
       <c r="XDH5" s="4"/>
       <c r="XDI5" s="4"/>
@@ -1243,31 +1277,31 @@
       <c r="XDM5" s="4"/>
       <c r="XDN5" s="4"/>
     </row>
-    <row r="6" spans="1:10 16335:16349" ht="39" customHeight="1">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="41"/>
-    </row>
-    <row r="7" spans="1:10 16335:16349" ht="39" customHeight="1">
-      <c r="A7" s="35" t="s">
+    <row r="6" spans="1:10 16335:16349" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="48"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="29"/>
+    </row>
+    <row r="7" spans="1:10 16335:16349" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
       <c r="XDG7" s="7"/>
       <c r="XDH7" s="7"/>
       <c r="XDI7" s="7"/>
@@ -1286,21 +1320,21 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:10 16335:16349" ht="39" customHeight="1">
+    <row r="8" spans="1:10 16335:16349" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="41"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="39"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
       <c r="XDG8" s="7"/>
       <c r="XDH8" s="7"/>
       <c r="XDI8" s="7"/>
@@ -1310,29 +1344,29 @@
       <c r="XDM8" s="6"/>
       <c r="XDN8" s="6"/>
     </row>
-    <row r="9" spans="1:10 16335:16349" ht="33.75" customHeight="1">
-      <c r="A9" s="36" t="s">
+    <row r="9" spans="1:10 16335:16349" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36" t="s">
+      <c r="F9" s="26"/>
+      <c r="G9" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36" t="s">
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26" t="s">
         <v>67</v>
       </c>
       <c r="XDG9" s="7"/>
@@ -1344,11 +1378,11 @@
       <c r="XDM9" s="6"/>
       <c r="XDN9" s="6"/>
     </row>
-    <row r="10" spans="1:10 16335:16349" s="24" customFormat="1" ht="34.5" customHeight="1">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="36"/>
+    <row r="10" spans="1:10 16335:16349" s="24" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="26"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="26"/>
       <c r="E10" s="25" t="s">
         <v>68</v>
       </c>
@@ -1364,7 +1398,7 @@
       <c r="I10" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="36"/>
+      <c r="J10" s="26"/>
       <c r="XDG10" s="4" t="s">
         <v>73</v>
       </c>
@@ -1391,7 +1425,7 @@
       </c>
       <c r="XDQ10" s="4"/>
     </row>
-    <row r="11" spans="1:10 16335:16349" ht="27" customHeight="1">
+    <row r="11" spans="1:10 16335:16349" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="22"/>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -1424,7 +1458,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:10 16335:16349" ht="27" customHeight="1">
+    <row r="12" spans="1:10 16335:16349" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -1442,7 +1476,7 @@
       <c r="XDM12" s="6"/>
       <c r="XDN12" s="6"/>
     </row>
-    <row r="13" spans="1:10 16335:16349" ht="33" customHeight="1">
+    <row r="13" spans="1:10 16335:16349" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1461,7 +1495,7 @@
       <c r="XDM13" s="6"/>
       <c r="XDN13" s="6"/>
     </row>
-    <row r="14" spans="1:10 16335:16349" ht="33" customHeight="1">
+    <row r="14" spans="1:10 16335:16349" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1480,7 +1514,7 @@
       <c r="XDM14" s="6"/>
       <c r="XDN14" s="6"/>
     </row>
-    <row r="15" spans="1:10 16335:16349" ht="33" customHeight="1">
+    <row r="15" spans="1:10 16335:16349" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -1499,7 +1533,7 @@
       <c r="XDM15" s="6"/>
       <c r="XDN15" s="6"/>
     </row>
-    <row r="16" spans="1:10 16335:16349" ht="33" customHeight="1">
+    <row r="16" spans="1:10 16335:16349" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -1518,7 +1552,7 @@
       <c r="XDM16" s="6"/>
       <c r="XDN16" s="6"/>
     </row>
-    <row r="17" spans="1:10 16335:16345" ht="33" customHeight="1">
+    <row r="17" spans="1:10 16335:16345" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -1537,7 +1571,7 @@
       <c r="XDM17" s="6"/>
       <c r="XDN17" s="6"/>
     </row>
-    <row r="18" spans="1:10 16335:16345" ht="33" customHeight="1">
+    <row r="18" spans="1:10 16335:16345" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -1556,7 +1590,7 @@
       <c r="XDM18" s="6"/>
       <c r="XDN18" s="6"/>
     </row>
-    <row r="19" spans="1:10 16335:16345" ht="33" customHeight="1">
+    <row r="19" spans="1:10 16335:16345" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -1575,7 +1609,7 @@
       <c r="XDM19" s="6"/>
       <c r="XDN19" s="6"/>
     </row>
-    <row r="20" spans="1:10 16335:16345" ht="33" customHeight="1">
+    <row r="20" spans="1:10 16335:16345" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -1594,19 +1628,19 @@
       <c r="XDM20" s="6"/>
       <c r="XDN20" s="6"/>
     </row>
-    <row r="21" spans="1:10 16335:16345" ht="34.5" customHeight="1">
-      <c r="A21" s="35" t="s">
+    <row r="21" spans="1:10 16335:16345" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
       <c r="XDG21" s="7"/>
       <c r="XDH21" s="7"/>
       <c r="XDI21" s="7"/>
@@ -1617,70 +1651,53 @@
       <c r="XDN21" s="6"/>
       <c r="XDQ21" s="4"/>
     </row>
-    <row r="22" spans="1:10 16335:16345" ht="33" customHeight="1">
-      <c r="A22" s="30" t="s">
+    <row r="22" spans="1:10 16335:16345" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="29" t="s">
+      <c r="B22" s="43"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="29"/>
+      <c r="E22" s="40"/>
       <c r="F22" s="15"/>
-      <c r="G22" s="29" t="s">
+      <c r="G22" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29" t="s">
+      <c r="H22" s="40"/>
+      <c r="I22" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="J22" s="29"/>
-    </row>
-    <row r="23" spans="1:10 16335:16345" ht="79.5" customHeight="1">
-      <c r="A23" s="39"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
+      <c r="J22" s="40"/>
+    </row>
+    <row r="23" spans="1:10 16335:16345" ht="79.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="44"/>
       <c r="F23" s="21"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-    </row>
-    <row r="26" spans="1:10 16335:16345" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="43" ht="15" customHeight="1"/>
-    <row r="44" ht="15" customHeight="1"/>
-    <row r="45" ht="15" customHeight="1"/>
-    <row r="46" ht="15" customHeight="1"/>
-    <row r="47" ht="15" customHeight="1"/>
-    <row r="50" ht="15" customHeight="1"/>
-    <row r="51" ht="15" customHeight="1"/>
-    <row r="52" ht="15" customHeight="1"/>
-    <row r="53" ht="15" customHeight="1"/>
-    <row r="54" ht="15" customHeight="1"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+    </row>
+    <row r="26" spans="1:10 16335:16345" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="42" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="43" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="50" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="51" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="B1:H2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:A2"/>
@@ -1697,6 +1714,23 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -1708,7 +1742,6 @@
 Construcción y Administración S.A./Sector Construcción&amp;R&amp;9Fecha de aprobación: 25.04.2022
 Pág. &amp;P de &amp;N </oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1724,15 +1757,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002CDB6831020C52409B02D6F92027612F" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ed3dab2221660d118cbb53b3c9fa8294">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2b230e36-0a53-4ac0-ac01-c22c1efbb34c" xmlns:ns3="e841f38b-9f23-43dc-9de2-cda5176cd52a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e335676877832fee96a691766106006" ns2:_="" ns3:_="">
     <xsd:import namespace="2b230e36-0a53-4ac0-ac01-c22c1efbb34c"/>
@@ -1993,14 +2017,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01A441AE-B7AC-46D9-99E9-6D0E1D379BF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01A441AE-B7AC-46D9-99E9-6D0E1D379BF6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2b230e36-0a53-4ac0-ac01-c22c1efbb34c"/>
+    <ds:schemaRef ds:uri="e841f38b-9f23-43dc-9de2-cda5176cd52a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2753ADF4-8A44-4C20-9D50-F9403D346684}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4902C612-16A9-44D6-AA9F-01B5EFF60A28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2b230e36-0a53-4ac0-ac01-c22c1efbb34c"/>
+    <ds:schemaRef ds:uri="e841f38b-9f23-43dc-9de2-cda5176cd52a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4902C612-16A9-44D6-AA9F-01B5EFF60A28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2753ADF4-8A44-4C20-9D50-F9403D346684}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>